--- a/src/main/resources/templates/OvertimeApply_add_Template.xlsx
+++ b/src/main/resources/templates/OvertimeApply_add_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\WorkSpace\New_HR\HR-11-codex\src\main\resources\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\WorkSpace\New_HR\HAE-VHR\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1145DF94-28F6-412E-ACDF-7D650D14FD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8101748E-A821-4093-BD5F-D5322E127F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6285" yWindow="2085" windowWidth="38700" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t xml:space="preserve">Employee ID </t>
   </si>
@@ -77,13 +77,34 @@
   </si>
   <si>
     <t>Nguyễn Văn A</t>
+  </si>
+  <si>
+    <t>Tên xe</t>
+  </si>
+  <si>
+    <t>Điểm đưa/đón</t>
+  </si>
+  <si>
+    <t>AFFIRMOR_ID_1/Người duyệt thứ 1</t>
+  </si>
+  <si>
+    <t>AFFIRMOR_ID_2/Người duyệt thứ 2</t>
+  </si>
+  <si>
+    <t>AFFIRMOR_ID_3/Người duyệt thứ 3</t>
+  </si>
+  <si>
+    <t>AFFIRMOR_ID_4/Người duyệt thứ 4</t>
+  </si>
+  <si>
+    <t>SIGN IN BY EMPLOYEE/Nhân viên tăng ca ký xác nhận</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,8 +139,20 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -135,6 +168,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -191,10 +230,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -213,9 +254,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{3E02AB36-6E9C-4077-B8BB-B9AA0D228A1A}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{82C0E5BA-0CD7-4A58-B701-748417933910}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -493,18 +540,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.28515625" customWidth="1"/>
     <col min="3" max="4" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" customWidth="1"/>
     <col min="6" max="6" width="27.42578125" customWidth="1"/>
-    <col min="7" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="27.42578125" customWidth="1"/>
+    <col min="7" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="11" width="20.85546875" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="26.5703125" customWidth="1"/>
+    <col min="14" max="14" width="27.42578125" customWidth="1"/>
+    <col min="15" max="19" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.5" customHeight="1">
+    <row r="1" spans="1:19" ht="25.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -532,11 +583,38 @@
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:19">
       <c r="A2" s="3">
         <v>43000001</v>
       </c>
@@ -565,8 +643,17 @@
         <v>0</v>
       </c>
       <c r="J2" s="3"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:19">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -577,8 +664,17 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:19">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -589,8 +685,17 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:19">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -601,8 +706,17 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:19">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -613,8 +727,17 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:19">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -625,8 +748,17 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:19">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -637,6 +769,15 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
